--- a/panchang-data/Vrindavan2026.xlsx
+++ b/panchang-data/Vrindavan2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5394">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16207,6 +16207,9 @@
   </si>
   <si>
     <t>121°05'03.58</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16696,7 +16699,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16782,7 +16785,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16868,7 +16871,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16954,7 +16957,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17040,7 +17043,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17126,7 +17129,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17212,7 +17215,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17298,7 +17301,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17384,7 +17387,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17470,7 +17473,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17556,7 +17559,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17642,7 +17645,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17728,7 +17731,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17814,7 +17817,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17900,7 +17903,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17986,7 +17989,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18072,7 +18075,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18158,7 +18161,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18244,7 +18247,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18330,7 +18333,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18416,7 +18419,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18502,7 +18505,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18588,7 +18591,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18674,7 +18677,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18760,7 +18763,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18846,7 +18849,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18932,7 +18935,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19018,7 +19021,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19104,7 +19107,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19190,7 +19193,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19276,7 +19279,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19362,7 +19365,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>564</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19448,7 +19451,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19534,7 +19537,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19620,7 +19623,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19706,7 +19709,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19792,7 +19795,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19878,7 +19881,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19964,7 +19967,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20050,7 +20053,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20136,7 +20139,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20222,7 +20225,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20308,7 +20311,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20394,7 +20397,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20480,7 +20483,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20566,7 +20569,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20652,7 +20655,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20738,7 +20741,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20824,7 +20827,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20910,7 +20913,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20996,7 +20999,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21082,7 +21085,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21168,7 +21171,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21254,7 +21257,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21340,7 +21343,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21426,7 +21429,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21512,7 +21515,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21598,7 +21601,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21684,7 +21687,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21770,7 +21773,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21856,7 +21859,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21942,7 +21945,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>564</v>
+        <v>1005</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22028,7 +22031,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22114,7 +22117,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22200,7 +22203,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22286,7 +22289,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22372,7 +22375,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22458,7 +22461,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22544,7 +22547,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22630,7 +22633,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22716,7 +22719,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22802,7 +22805,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22888,7 +22891,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22974,7 +22977,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23060,7 +23063,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23146,7 +23149,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23232,7 +23235,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23318,7 +23321,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23404,7 +23407,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23490,7 +23493,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23576,7 +23579,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23662,7 +23665,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23748,7 +23751,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23834,7 +23837,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23920,7 +23923,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24006,7 +24009,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24092,7 +24095,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24178,7 +24181,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24264,7 +24267,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24350,7 +24353,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24436,7 +24439,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24522,7 +24525,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1005</v>
+        <v>1446</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24608,7 +24611,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24694,7 +24697,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24780,7 +24783,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24866,7 +24869,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24952,7 +24955,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25038,7 +25041,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25124,7 +25127,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25210,7 +25213,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25296,7 +25299,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25382,7 +25385,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25468,7 +25471,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25554,7 +25557,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25640,7 +25643,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25726,7 +25729,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25812,7 +25815,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25898,7 +25901,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25984,7 +25987,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26070,7 +26073,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26156,7 +26159,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26242,7 +26245,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26328,7 +26331,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26414,7 +26417,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26500,7 +26503,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26586,7 +26589,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26672,7 +26675,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26758,7 +26761,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26844,7 +26847,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26930,7 +26933,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27016,7 +27019,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1446</v>
+        <v>1868</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27102,7 +27105,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27188,7 +27191,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27274,7 +27277,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27360,7 +27363,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27446,7 +27449,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27532,7 +27535,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27618,7 +27621,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27704,7 +27707,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27790,7 +27793,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27876,7 +27879,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27962,7 +27965,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28048,7 +28051,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28134,7 +28137,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28220,7 +28223,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28306,7 +28309,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1868</v>
+        <v>2305</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28392,7 +28395,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28478,7 +28481,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28564,7 +28567,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28650,7 +28653,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28736,7 +28739,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28822,7 +28825,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28908,7 +28911,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28994,7 +28997,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29080,7 +29083,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29166,7 +29169,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29252,7 +29255,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29338,7 +29341,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29424,7 +29427,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29510,7 +29513,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29596,7 +29599,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1868</v>
+        <v>5393</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29682,7 +29685,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29768,7 +29771,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29854,7 +29857,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29940,7 +29943,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30026,7 +30029,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30112,7 +30115,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30198,7 +30201,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30284,7 +30287,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30370,7 +30373,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30456,7 +30459,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30542,7 +30545,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30628,7 +30631,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30714,7 +30717,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30800,7 +30803,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30886,7 +30889,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2305</v>
+        <v>5393</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
